--- a/data/trans_orig/P55S_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P55S_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2007</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2007 (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -846,97 +846,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1748</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1066</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5247</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5851</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31204</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>37934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53505</t>
+          <t>52409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>67848</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -1415,97 +1415,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1083</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5524</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46038</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41569</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56359</t>
+          <t>57147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82853</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>99538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -1984,97 +1984,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5616</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>6249</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5786</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4981</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39518</t>
+          <t>38844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55353</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>24581</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32564</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36102</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>52581</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49252</t>
+          <t>49827</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69084</t>
+          <t>68957</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23059</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>37231</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61848</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94694</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111702</t>
+          <t>111202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141019</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170242</t>
+          <t>170169</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>243502</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>277501</t>
+          <t>276184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>33965</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2012</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2012 (tasa de respuesta: 97,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22632</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>31507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46835</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73226</t>
+          <t>73839</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -4149,62 +4149,62 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5840</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7310</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>29401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>69587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80471</t>
+          <t>81172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102605</t>
+          <t>102763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45791</t>
+          <t>45601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64059</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22068</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34806</t>
+          <t>34401</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33628</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50996</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>60550</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>83040</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>70,19%</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31582</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>57212</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47815</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79613</t>
+          <t>79054</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39995</t>
+          <t>40282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66695</t>
+          <t>67456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83366</t>
+          <t>81041</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94784</t>
+          <t>95066</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118213</t>
+          <t>118364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161120</t>
+          <t>160443</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>194604</t>
+          <t>194581</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265540</t>
+          <t>264910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307343</t>
+          <t>304739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2016</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2016 (tasa de respuesta: 96,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46480</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65992</t>
+          <t>66517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37584</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48700</t>
+          <t>47960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81673</t>
+          <t>80877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99718</t>
+          <t>99588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39895</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44898</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>60640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -8364,97 +8364,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6580</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>2067</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6643</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>7466</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>7249</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26076</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40744</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59960</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>62489</t>
+          <t>62290</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83546</t>
+          <t>84093</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58628</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>45469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77914</t>
+          <t>75345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>33425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>85574</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>103693</t>
+          <t>102806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164756</t>
+          <t>161820</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197482</t>
+          <t>196479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>255990</t>
+          <t>256971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>294236</t>
+          <t>294292</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37119</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2023</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32033</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33732</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30569</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>47547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59067</t>
+          <t>59317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74576</t>
+          <t>75104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>20726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>30086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43385</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>55590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67955</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83684</t>
+          <t>82887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>19293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>28832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>57484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>32232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15243</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27380</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32632</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>64853</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>79491</t>
+          <t>79942</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>97955</t>
+          <t>98085</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57772</t>
+          <t>56963</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56100</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79053</t>
+          <t>78408</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>39990</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>70747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93053</t>
+          <t>93233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99572</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>128522</t>
+          <t>127441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87318</t>
+          <t>86949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105886</t>
+          <t>106047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>171579</t>
+          <t>173191</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197245</t>
+          <t>199055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265036</t>
+          <t>265981</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>296997</t>
+          <t>298555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P55S_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P55S_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37934</t>
+          <t>37352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>53297</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67848</t>
+          <t>67924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22349</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45234</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57147</t>
+          <t>57212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81667</t>
+          <t>81768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99538</t>
+          <t>99761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>55261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>32135</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36340</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>53095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49827</t>
+          <t>49954</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68957</t>
+          <t>69158</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93830</t>
+          <t>95517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>142671</t>
+          <t>143405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>171563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>242664</t>
+          <t>243818</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>276184</t>
+          <t>276047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29595</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>31434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46704</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54999</t>
+          <t>54701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73839</t>
+          <t>72533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51594</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69587</t>
+          <t>68479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81172</t>
+          <t>80650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102763</t>
+          <t>102313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18557</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27313</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>63683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>37517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22068</t>
+          <t>22475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51355</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60550</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83040</t>
+          <t>82985</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>46865</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79054</t>
+          <t>77622</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67456</t>
+          <t>67903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81041</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95066</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118364</t>
+          <t>117915</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160443</t>
+          <t>161679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>194581</t>
+          <t>194899</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264910</t>
+          <t>264053</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304739</t>
+          <t>302962</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46248</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47960</t>
+          <t>48503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64618</t>
+          <t>64943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80877</t>
+          <t>80733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99588</t>
+          <t>99710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25382</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>44688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32267</t>
+          <t>32536</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>40579</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>62290</t>
+          <t>62204</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84093</t>
+          <t>83880</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>17155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>40914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85574</t>
+          <t>86182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102806</t>
+          <t>102965</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>163000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>196479</t>
+          <t>197302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256971</t>
+          <t>256240</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>294292</t>
+          <t>293586</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>43377</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48857</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>26790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>44960</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47547</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>66911</t>
+          <t>71751</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>80446</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49626</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49626</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49626</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79673</t>
+          <t>84874</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79673</t>
+          <t>84874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79673</t>
+          <t>84874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>129298</t>
+          <t>137871</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129298</t>
+          <t>137871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129298</t>
+          <t>137871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>31618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>33342</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42897</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55590</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82887</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>124690</t>
+          <t>136492</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124690</t>
+          <t>136492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124690</t>
+          <t>136492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19293</t>
+          <t>23022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>33623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40204</t>
+          <t>45993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>58388</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>66373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>29707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>29707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>29707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>64898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>64898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>64898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25230</t>
+          <t>28904</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33071</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31382</t>
+          <t>32210</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57469</t>
+          <t>61450</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64853</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>93659</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>79942</t>
+          <t>83317</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98085</t>
+          <t>102680</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>104266</t>
+          <t>112832</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104266</t>
+          <t>112832</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104266</t>
+          <t>112832</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>147494</t>
+          <t>157395</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>147494</t>
+          <t>157395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147494</t>
+          <t>157395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>29611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46719</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56963</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>67127</t>
+          <t>73016</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78408</t>
+          <t>86615</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>42969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70747</t>
+          <t>77410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93233</t>
+          <t>99502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>121282</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>107829</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127441</t>
+          <t>136101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>97360</t>
+          <t>105391</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86949</t>
+          <t>94890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106047</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>184717</t>
+          <t>201256</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173191</t>
+          <t>188291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>199055</t>
+          <t>213580</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>282077</t>
+          <t>306647</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265981</t>
+          <t>288067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>298555</t>
+          <t>322803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>357241</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>357241</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>357241</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>485321</t>
+          <t>526362</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>485321</t>
+          <t>526362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>485321</t>
+          <t>526362</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
